--- a/examples/本地验收报告/综合部督办报告.xlsx
+++ b/examples/本地验收报告/综合部督办报告.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'风险分布'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'拖延原因'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'部门完成情况'!$A$1:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务清单'!$A$1:$AF$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务清单'!$A$1:$AF$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'重点任务'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'逾期任务'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'协办任务'!$A$1:$AF$1</definedName>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.3333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -909,9 +909,7 @@
           <t>按期完成率</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="B8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -930,7 +928,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1048,31 +1046,29 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -1179,31 +1175,29 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0</v>
@@ -1251,7 +1245,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:08:09+08:00</t>
+          <t>2026-10-17T15:27:04+08:00</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1347,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -1393,7 +1387,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1403,7 +1397,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1444,7 +1438,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1454,7 +1448,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1521,11 +1515,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>尚未研判</t>
+          <t>信息不足</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1566,7 +1560,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1581,7 +1575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF5"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1783,12 +1777,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ef8955a87e994e0db9229ecdc1793382</t>
+          <t>74dbf809d8d04f93b4de207464b9b7fd</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>测试并发事项0</t>
+          <t>测试原生综合部交付</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1804,7 +1798,7 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-11-16</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
@@ -1814,13 +1808,17 @@
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:08:06+08:00</t>
+          <t>2026-10-17T15:26:51+08:00</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
@@ -1830,14 +1828,30 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>测试初始进展</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:56+08:00</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="n">
@@ -1848,12 +1862,12 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:08:06+08:00</t>
+          <t>2026-10-17T15:26:51+08:00</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:08:06+08:00</t>
+          <t>2026-10-17T15:26:51+08:00</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
@@ -1862,266 +1876,8 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2e1a3d8143d1433f806973c834c51104</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>测试并发事项1</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>综合部</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026-11-16</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>未开始</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>管理员</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:08:06+08:00</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>管理员</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>53918a8e99e84a1db7ae6f4b88f1095a</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>测试流程材料</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>综合部</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>材料已归档</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr"/>
-      <c r="V4" s="2" t="inlineStr"/>
-      <c r="W4" s="2" t="inlineStr"/>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AE4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AF4" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>9bf1c703214a411d9fb929ae43eeeacd</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>测试取消事项</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>综合部</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>已取消</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr"/>
-      <c r="V5" s="2" t="inlineStr"/>
-      <c r="W5" s="2" t="inlineStr"/>
-      <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AE5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AF5" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AF5"/>
+  <autoFilter ref="A1:AF2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
